--- a/data/trans_dic/IP11C$ingresado-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,73</t>
+          <t>0,0; 69,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,16</t>
+          <t>0,0; 58,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,58</t>
+          <t>0,0; 74,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,04</t>
+          <t>0,0; 25,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,93</t>
+          <t>0,0; 41,81</t>
         </is>
       </c>
     </row>
@@ -856,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,39</t>
+          <t>0,0; 33,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,29</t>
+          <t>0,0; 54,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,94</t>
+          <t>0,0; 40,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,84</t>
+          <t>0,0; 44,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,27</t>
+          <t>0,0; 28,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,02</t>
+          <t>0,0; 26,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,99</t>
+          <t>0,0; 45,97</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,03</t>
+          <t>0,0; 46,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,48</t>
+          <t>0,0; 42,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,46</t>
+          <t>0,0; 28,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 29,68</t>
+          <t>2,97; 31,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,41</t>
+          <t>0,0; 37,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,55</t>
+          <t>0,0; 52,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,99</t>
+          <t>0,0; 24,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,43</t>
+          <t>0,0; 12,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 21,92</t>
+          <t>3,18; 21,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,83</t>
+          <t>0,0; 19,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,62</t>
+          <t>0,0; 25,23</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,25</t>
+          <t>0,0; 40,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,13</t>
+          <t>0,0; 33,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,66</t>
+          <t>0,0; 37,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,96</t>
+          <t>0,0; 43,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,21</t>
+          <t>0,0; 27,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,35</t>
+          <t>0,0; 19,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,74</t>
+          <t>0,0; 36,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,0</t>
+          <t>0,0; 30,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,21</t>
+          <t>0,0; 25,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,51</t>
+          <t>0,0; 11,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,52</t>
+          <t>1,34; 12,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 19,5</t>
+          <t>2,1; 22,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 26,27</t>
+          <t>2,48; 29,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,18</t>
+          <t>1,34; 12,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 14,23</t>
+          <t>2,79; 14,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,42</t>
+          <t>0,0; 14,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,21</t>
+          <t>0,0; 14,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 9,07</t>
+          <t>1,25; 9,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 10,31</t>
+          <t>3,06; 10,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 12,61</t>
+          <t>1,8; 13,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 15,48</t>
+          <t>2,72; 15,29</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2425</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2316</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2697</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2476</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2989</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2618</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2533</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3070</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3784</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3188</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3271</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4493</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4480</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2658</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2719</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1857</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1096</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1881</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3738</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1096</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3586</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>471; 5035</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3029</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2770</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5952</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3400</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1274; 8616</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3999</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3146</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1680</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1680</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1692</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2673</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3752</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5135</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3853</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3867</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5304</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5597</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2818</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2875</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2484</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1741</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>5014</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3294</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3947</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>665; 6155</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>465; 4919</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>426; 5006</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>605; 5751</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1990; 10419</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 6094</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3587</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>987; 7361</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3704; 13191</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1130; 8183</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1118; 6299</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$ingresado-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Clase-trans_dic.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,06</t>
+          <t>0,0; 66,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,49</t>
+          <t>0,0; 57,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,16</t>
+          <t>0,0; 68,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,22</t>
+          <t>0,0; 22,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,81</t>
+          <t>0,0; 48,48</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,98</t>
+          <t>0,0; 34,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,54</t>
+          <t>0,0; 60,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,14</t>
+          <t>0,0; 39,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,19</t>
+          <t>0,0; 46,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,04</t>
+          <t>0,0; 29,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,23</t>
+          <t>0,0; 24,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,97</t>
+          <t>0,0; 47,4</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,73</t>
+          <t>0,0; 46,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,6</t>
+          <t>0,0; 48,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,2</t>
+          <t>0,0; 27,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 31,76</t>
+          <t>2,94; 28,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,69</t>
+          <t>0,0; 36,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,07</t>
+          <t>0,0; 57,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,54</t>
+          <t>0,0; 25,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,48</t>
+          <t>0,0; 12,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 21,48</t>
+          <t>3,13; 21,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,63</t>
+          <t>0,0; 17,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,23</t>
+          <t>0,0; 27,46</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,57</t>
+          <t>0,0; 42,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,53</t>
+          <t>0,0; 34,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,93</t>
+          <t>0,0; 36,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,61</t>
+          <t>0,0; 47,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,53</t>
+          <t>0,0; 30,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,79</t>
+          <t>0,0; 19,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,29</t>
+          <t>0,0; 36,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,53</t>
+          <t>0,0; 35,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,5</t>
+          <t>0,0; 29,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,58</t>
+          <t>0,0; 11,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 12,37</t>
+          <t>1,35; 11,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 22,24</t>
+          <t>2,13; 19,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 29,19</t>
+          <t>2,32; 26,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 12,73</t>
+          <t>1,43; 12,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 14,58</t>
+          <t>2,82; 14,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,96</t>
+          <t>0,0; 14,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,93</t>
+          <t>0,0; 15,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 9,29</t>
+          <t>1,44; 8,78</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 10,88</t>
+          <t>3,03; 11,03</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 13,02</t>
+          <t>1,8; 13,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,29</t>
+          <t>2,8; 16,65</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2425</t>
+          <t>0; 2353</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2316</t>
+          <t>0; 2279</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2697</t>
+          <t>0; 2488</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2476</t>
+          <t>0; 2214</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2989</t>
+          <t>0; 3466</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2618</t>
+          <t>0; 2621</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3070</t>
+          <t>0; 3410</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3784</t>
+          <t>0; 3747</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,17 +2170,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3188</t>
+          <t>0; 3364</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3271</t>
+          <t>0; 3450</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4493</t>
+          <t>0; 4142</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4480</t>
+          <t>0; 4620</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2658</t>
+          <t>0; 2649</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2719</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2551,22 +2551,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3586</t>
+          <t>0; 3497</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>471; 5035</t>
+          <t>466; 4582</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3029</t>
+          <t>0; 2970</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2770</t>
+          <t>0; 3048</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5952</t>
+          <t>0; 6254</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3400</t>
+          <t>0; 3344</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1274; 8616</t>
+          <t>1254; 8678</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 3999</t>
+          <t>0; 3555</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3146</t>
+          <t>0; 3425</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2673</t>
+          <t>0; 2769</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3752</t>
+          <t>0; 3900</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5135</t>
+          <t>0; 4892</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3853</t>
+          <t>0; 4159</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2799,17 +2799,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3867</t>
+          <t>0; 4338</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 5304</t>
+          <t>0; 5191</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5597</t>
+          <t>0; 5661</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2818</t>
+          <t>0; 3303</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 2875</t>
+          <t>0; 3334</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3947</t>
+          <t>0; 3939</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>665; 6155</t>
+          <t>673; 5694</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>465; 4919</t>
+          <t>472; 4408</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>426; 5006</t>
+          <t>398; 4493</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>605; 5751</t>
+          <t>648; 5841</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1990; 10419</t>
+          <t>2015; 10463</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6094</t>
+          <t>0; 5980</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3587</t>
+          <t>0; 3831</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>987; 7361</t>
+          <t>1145; 6956</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3704; 13191</t>
+          <t>3676; 13370</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1130; 8183</t>
+          <t>1133; 8366</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1118; 6299</t>
+          <t>1151; 6858</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$ingresado-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 59,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,99</t>
+          <t>0,0; 79,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,41</t>
+          <t>0,0; 64,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,56</t>
+          <t>0,0; 24,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,48</t>
+          <t>0,0; 44,36</t>
         </is>
       </c>
     </row>
@@ -789,34 +789,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>8,14%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 56,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,02</t>
+          <t>0,0; 38,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,37 +872,37 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 41,42</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 36,39</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 60,58</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 39,74</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 46,64</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,57</t>
+          <t>0,0; 34,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,18</t>
+          <t>0,0; 25,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,4</t>
+          <t>0,0; 42,03</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 47,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,16</t>
+          <t>0,0; 42,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,8%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11,71%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 28,9</t>
+          <t>0,0; 26,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 28,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,78</t>
+          <t>3,03; 29,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 43,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,27</t>
+          <t>0,0; 13,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 21,64</t>
+          <t>3,03; 21,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,45</t>
+          <t>0,0; 17,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,46</t>
+          <t>0,0; 26,46</t>
         </is>
       </c>
     </row>
@@ -1209,37 +1209,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>11,85%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>9,78%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,41%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 34,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 41,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,02</t>
+          <t>0,0; 46,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,08</t>
+          <t>0,0; 40,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,88</t>
+          <t>0,0; 28,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,37</t>
+          <t>0,0; 19,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,7</t>
+          <t>0,0; 34,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 33,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,57</t>
+          <t>0,0; 31,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2,16%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4,99%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>7,87%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,56</t>
+          <t>1,44; 13,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,44</t>
+          <t>3,14; 14,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 19,93</t>
+          <t>0,0; 13,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 26,2</t>
+          <t>0,0; 15,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,93</t>
+          <t>0,0; 10,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 14,64</t>
+          <t>1,36; 11,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,68</t>
+          <t>2,13; 19,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,94</t>
+          <t>2,09; 25,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,78</t>
+          <t>1,46; 9,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 11,03</t>
+          <t>2,94; 10,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 13,31</t>
+          <t>1,98; 12,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 16,65</t>
+          <t>2,2; 15,23</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>488</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1874,34 +1874,34 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>488</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>819</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2343</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2353</t>
+          <t>0; 2659</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2279</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2488</t>
+          <t>0; 2254</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2214</t>
+          <t>0; 2360</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3466</t>
+          <t>0; 3033</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2067,49 +2067,49 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>832</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>832</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>779</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>1406</t>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1293</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3168</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2621</t>
+          <t>0; 3671</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2533</t>
+          <t>0; 2782</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3410</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3747</t>
+          <t>0; 2803</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,17 +2170,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3364</t>
+          <t>0; 2569</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3450</t>
+          <t>0; 3998</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4142</t>
+          <t>0; 4286</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4620</t>
+          <t>0; 3904</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2675</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2649</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3074</t>
+          <t>0; 2712</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1881</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1857</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1096</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1881</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>592</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>592</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3497</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>466; 4582</t>
+          <t>0; 6547</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3048</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3620</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6254</t>
+          <t>480; 4705</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3489</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2876</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3344</t>
+          <t>0; 3661</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1254; 8678</t>
+          <t>1216; 8790</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 3555</t>
+          <t>0; 3632</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3425</t>
+          <t>0; 3067</t>
         </is>
       </c>
     </row>
@@ -2623,12 +2623,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2691,37 +2691,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>644</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1680</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3819</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5640</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2769</t>
+          <t>0; 4149</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3900</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4892</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4159</t>
+          <t>0; 2652</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2799,17 +2799,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4338</t>
+          <t>0; 3962</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 5191</t>
+          <t>0; 5185</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5661</t>
+          <t>0; 5358</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>674</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3046</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3303</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 3334</t>
+          <t>0; 3518</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5014</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2484</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>1740</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2557</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>5014</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1673</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2705</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3939</t>
+          <t>652; 5951</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>673; 5694</t>
+          <t>2243; 10166</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>472; 4408</t>
+          <t>0; 5466</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>398; 4493</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>648; 5841</t>
+          <t>0; 3583</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2015; 10463</t>
+          <t>676; 5734</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 5980</t>
+          <t>471; 4314</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3831</t>
+          <t>359; 4385</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1145; 6956</t>
+          <t>1160; 7184</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3676; 13370</t>
+          <t>3560; 12495</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1133; 8366</t>
+          <t>1246; 7923</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1151; 6858</t>
+          <t>869; 6005</t>
         </is>
       </c>
     </row>
